--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -517,7 +517,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -648,7 +648,7 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -907,7 +907,7 @@
     <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類2．身体計測の「焦点」</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -962,7 +962,7 @@
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -986,7 +986,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1014,7 +1014,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1034,7 +1034,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1117,7 +1117,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1221,7 +1221,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1273,7 +1273,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1303,7 +1303,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1315,7 +1315,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1340,7 +1340,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1415,7 +1415,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1465,7 +1465,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1498,7 +1498,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1535,7 +1535,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1554,7 +1554,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1609,7 +1609,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2004,7 +2004,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.51953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -517,7 +517,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -648,7 +648,7 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -907,7 +907,7 @@
     <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類2．身体計測の「焦点」</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -962,7 +962,7 @@
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -986,7 +986,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1014,7 +1014,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1034,7 +1034,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1117,7 +1117,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1221,7 +1221,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1273,7 +1273,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1303,7 +1303,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1315,7 +1315,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1340,7 +1340,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1415,7 +1415,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1465,7 +1465,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1498,7 +1498,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1535,7 +1535,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement)
 </t>
   </si>
   <si>
@@ -1554,7 +1554,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement|1.3.0-dev)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_BodyMeasurement)
 </t>
   </si>
   <si>
@@ -1609,7 +1609,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2004,7 +2004,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="68.046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.51953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
